--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/data inputs/jeans/Product-Description-inputs.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/data inputs/jeans/Product-Description-inputs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\jeans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8B626B-D82C-4A84-8858-022B69072F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359D245D-2C20-43EE-AEDE-75C0A3630905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="52">
   <si>
     <t>kind</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>WPJ-NY-</t>
+  </si>
+  <si>
+    <t>White-Baggy</t>
   </si>
 </sst>
 </file>
@@ -1129,19 +1132,54 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
